--- a/public/docs/Template_Shikake_Dbl_Crimp.xlsx
+++ b/public/docs/Template_Shikake_Dbl_Crimp.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>Carline</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Address</t>
+  </si>
+  <si>
+    <t>Address Store</t>
   </si>
   <si>
     <t>Barcode Mesin</t>
@@ -453,7 +456,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="0"/>
@@ -466,21 +469,22 @@
     <col min="8" max="8" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="19.852" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="19.852" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="13.997" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,6 +550,9 @@
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
